--- a/interim/cluster_review.xlsx
+++ b/interim/cluster_review.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilya/chat-geospatial/interim/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB17067E-1E7C-9D4B-B04B-FD2CD5B771A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A886A0-5B63-D644-810A-41C5032113AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16840" yWindow="600" windowWidth="33480" windowHeight="26900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7220" yWindow="600" windowWidth="33480" windowHeight="26900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$110</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -1057,18 +1057,9 @@
     <t>Beach + social media copy</t>
   </si>
   <si>
-    <t>US presidents &amp; elections</t>
-  </si>
-  <si>
     <t>Turkey</t>
   </si>
   <si>
-    <t>UK &amp; French monarchs / heads of state</t>
-  </si>
-  <si>
-    <t>Prime ministers</t>
-  </si>
-  <si>
     <t>Noisy cluster</t>
   </si>
   <si>
@@ -1105,12 +1096,6 @@
     <t>Queries suggest use of llm as agent</t>
   </si>
   <si>
-    <t>Airports</t>
-  </si>
-  <si>
-    <t>Restaurants</t>
-  </si>
-  <si>
     <t>China &amp; Taiwan</t>
   </si>
   <si>
@@ -1135,9 +1120,6 @@
     <t>Property description &amp; search</t>
   </si>
   <si>
-    <t>Addresses and ZIP codes</t>
-  </si>
-  <si>
     <t>Germany</t>
   </si>
   <si>
@@ -1147,15 +1129,9 @@
     <t>Capital cities</t>
   </si>
   <si>
-    <t>Historical battles &amp; wars</t>
-  </si>
-  <si>
     <t>What if / hypothetical history scenarios</t>
   </si>
   <si>
-    <t>European history</t>
-  </si>
-  <si>
     <t>Religion</t>
   </si>
   <si>
@@ -1171,9 +1147,6 @@
     <t>Paris specifically</t>
   </si>
   <si>
-    <t>US history</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -1216,9 +1189,6 @@
     <t>GeoGuessr &amp; map projections</t>
   </si>
   <si>
-    <t>Plants, animals &amp; wildlife by region</t>
-  </si>
-  <si>
     <t>US states and places</t>
   </si>
   <si>
@@ -1231,12 +1201,6 @@
     <t>cluster based on 'redacted' keyword</t>
   </si>
   <si>
-    <t>GDP &amp; national economies</t>
-  </si>
-  <si>
-    <t>Volcanoes, rocks, geology</t>
-  </si>
-  <si>
     <t>India</t>
   </si>
   <si>
@@ -1279,30 +1243,9 @@
     <t>Canada</t>
   </si>
   <si>
-    <t>Weather &amp; temperature</t>
-  </si>
-  <si>
     <t>Write a script (university/college focus)</t>
   </si>
   <si>
-    <t>Time zones</t>
-  </si>
-  <si>
-    <t>Tall buildings &amp; towers</t>
-  </si>
-  <si>
-    <t>Mountains &amp; elevation</t>
-  </si>
-  <si>
-    <t>Planets &amp; space</t>
-  </si>
-  <si>
-    <t>University rankings</t>
-  </si>
-  <si>
-    <t>Oceans, water &amp; hydrology</t>
-  </si>
-  <si>
     <t>group</t>
   </si>
   <si>
@@ -1312,42 +1255,6 @@
     <t>Trip planning</t>
   </si>
   <si>
-    <t>Country-specific questions</t>
-  </si>
-  <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Temporal</t>
-  </si>
-  <si>
-    <t>Administrative</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Cultural</t>
-  </si>
-  <si>
-    <t>POIs &amp; Commercial</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>Historical</t>
-  </si>
-  <si>
-    <t>Biographical</t>
-  </si>
-  <si>
-    <t>Birthplaces &amp; residences</t>
-  </si>
-  <si>
-    <t>Physical</t>
-  </si>
-  <si>
     <t>Write an analysis</t>
   </si>
   <si>
@@ -1696,16 +1603,109 @@
     <t>write a limerick about new zealand</t>
   </si>
   <si>
-    <t>Write a (university) application / cover letter</t>
-  </si>
-  <si>
     <t>africa focus</t>
   </si>
   <si>
-    <t>Presidents</t>
-  </si>
-  <si>
     <t>latin america focus</t>
+  </si>
+  <si>
+    <t>Write an application / cover letter</t>
+  </si>
+  <si>
+    <t>POIs &amp; Commercial*</t>
+  </si>
+  <si>
+    <t>Country-specific</t>
+  </si>
+  <si>
+    <t>Physical*</t>
+  </si>
+  <si>
+    <t>Historical*</t>
+  </si>
+  <si>
+    <t>Events*</t>
+  </si>
+  <si>
+    <t>Temporal*</t>
+  </si>
+  <si>
+    <t>Administrative*</t>
+  </si>
+  <si>
+    <t>Statistical*</t>
+  </si>
+  <si>
+    <t>Cultural*</t>
+  </si>
+  <si>
+    <t>Biographical*</t>
+  </si>
+  <si>
+    <t>Addresses and ZIP codes*</t>
+  </si>
+  <si>
+    <t>Airports*</t>
+  </si>
+  <si>
+    <t>Birthplaces &amp; residences*</t>
+  </si>
+  <si>
+    <t>European history*</t>
+  </si>
+  <si>
+    <t>Planets &amp; space*</t>
+  </si>
+  <si>
+    <t>GDP &amp; national economies*</t>
+  </si>
+  <si>
+    <t>Historical battles &amp; wars*</t>
+  </si>
+  <si>
+    <t>Mountains &amp; elevation*</t>
+  </si>
+  <si>
+    <t>Oceans, water &amp; hydrology*</t>
+  </si>
+  <si>
+    <t>Plants, animals &amp; wildlife by region*</t>
+  </si>
+  <si>
+    <t>Presidents*</t>
+  </si>
+  <si>
+    <t>Prime ministers*</t>
+  </si>
+  <si>
+    <t>Restaurants*</t>
+  </si>
+  <si>
+    <t>Tall buildings &amp; towers*</t>
+  </si>
+  <si>
+    <t>Time zones*</t>
+  </si>
+  <si>
+    <t>UK &amp; French monarchs / heads of state*</t>
+  </si>
+  <si>
+    <t>University rankings*</t>
+  </si>
+  <si>
+    <t>US history*</t>
+  </si>
+  <si>
+    <t>US presidents &amp; elections*</t>
+  </si>
+  <si>
+    <t>Volcanoes, rocks, geology*</t>
+  </si>
+  <si>
+    <t>Weather &amp; temperature*</t>
+  </si>
+  <si>
+    <t>Misc</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1733,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1755,6 +1755,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1797,7 +1803,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1814,7 +1820,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2128,7 +2135,7 @@
     <col min="6" max="6" width="38.5" style="3" customWidth="1"/>
     <col min="7" max="7" width="29.5" style="5" customWidth="1"/>
     <col min="8" max="8" width="31.33203125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="57.5" customWidth="1"/>
+    <col min="9" max="9" width="57.5" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -2151,441 +2158,444 @@
         <v>332</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="I1" t="s">
-        <v>450</v>
+      <c r="I1" s="8" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>356</v>
+        <v>538</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>451</v>
+        <v>534</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>221</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>222</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>223</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>221</v>
+        <v>534</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B4">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>452</v>
+        <v>534</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B5">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>453</v>
+        <v>534</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B6">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>454</v>
+        <v>534</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B7">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>254</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>255</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>256</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>342</v>
+        <v>387</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>455</v>
+        <v>534</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B8">
-        <v>158</v>
+        <v>374</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>348</v>
+        <v>540</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>456</v>
+        <v>537</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B9">
-        <v>374</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>457</v>
+        <v>410</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>320</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>322</v>
+        <v>22</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>458</v>
+        <v>448</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B11">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="D11" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="E11" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>416</v>
+        <v>491</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>459</v>
+        <v>410</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="B12">
-        <v>66</v>
+        <v>387</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>317</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>318</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>319</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>460</v>
+        <v>410</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="B13">
-        <v>62</v>
+        <v>281</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>314</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>315</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>316</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>461</v>
+        <v>410</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="B14">
-        <v>177</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>284</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>285</v>
       </c>
       <c r="E14" t="s">
-        <v>187</v>
+        <v>286</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>462</v>
+        <v>410</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B15">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D15" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>463</v>
+        <v>529</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B16">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D16" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="E16" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>311</v>
+        <v>529</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="B17">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>323</v>
       </c>
       <c r="D17" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="E17" t="s">
-        <v>226</v>
+        <v>325</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>464</v>
+        <v>529</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2605,1761 +2615,1782 @@
         <v>109</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>465</v>
+        <v>529</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="B19">
-        <v>899</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>155</v>
       </c>
       <c r="D19" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
-        <v>259</v>
+        <v>157</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>466</v>
+        <v>529</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B20">
-        <v>88</v>
+        <v>311</v>
       </c>
       <c r="C20" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="D20" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="E20" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>467</v>
+        <v>529</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B21">
-        <v>384</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>177</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>468</v>
+        <v>529</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B22">
-        <v>254</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>408</v>
+        <v>347</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>469</v>
+        <v>529</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B23">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="D23" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="E23" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>529</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="B24">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="C24" t="s">
-        <v>230</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>231</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>232</v>
+        <v>91</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="I24" t="s">
-        <v>471</v>
+        <v>529</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A25">
+        <v>26</v>
+      </c>
+      <c r="B25">
         <v>96</v>
       </c>
-      <c r="B25">
-        <v>145</v>
-      </c>
       <c r="C25" t="s">
-        <v>296</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>297</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>298</v>
+        <v>88</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>408</v>
+        <v>351</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>472</v>
+        <v>529</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B26">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>473</v>
+        <v>529</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B27">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="D27" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="E27" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>474</v>
+        <v>529</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B28">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>475</v>
+        <v>529</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="B29">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>278</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>279</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>280</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>476</v>
+        <v>392</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>480</v>
+        <v>529</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B30">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>477</v>
+        <v>349</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>481</v>
+        <v>529</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="B31">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
+        <v>168</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>482</v>
+        <v>529</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="B32">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>267</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>268</v>
+        <v>112</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>401</v>
+        <v>357</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>483</v>
+        <v>529</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="B33">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C33" t="s">
-        <v>248</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>249</v>
+        <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>395</v>
+        <v>343</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>484</v>
+        <v>529</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="B34">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>485</v>
+        <v>529</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B35">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="C35" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>486</v>
+        <v>536</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="B36">
-        <v>206</v>
+        <v>67</v>
       </c>
       <c r="C36" t="s">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="E36" t="s">
-        <v>301</v>
+        <v>85</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>409</v>
+        <v>350</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>487</v>
+        <v>536</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="B37">
-        <v>311</v>
+        <v>177</v>
       </c>
       <c r="C37" t="s">
-        <v>275</v>
+        <v>29</v>
       </c>
       <c r="D37" t="s">
-        <v>276</v>
+        <v>30</v>
       </c>
       <c r="E37" t="s">
-        <v>277</v>
+        <v>31</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>403</v>
+        <v>338</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>488</v>
+        <v>532</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B38">
-        <v>55</v>
+        <v>345</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="D38" t="s">
-        <v>33</v>
+        <v>204</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>489</v>
+        <v>532</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B39">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>490</v>
+        <v>532</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B40">
-        <v>122</v>
+        <v>384</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E40" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>377</v>
+        <v>541</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>491</v>
+        <v>531</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B41">
-        <v>239</v>
+        <v>63</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="E41" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>355</v>
+        <v>544</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>492</v>
+        <v>531</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B42">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E42" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>354</v>
+        <v>548</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>493</v>
+        <v>531</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B43">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>364</v>
+        <v>549</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>494</v>
+        <v>531</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B44">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>242</v>
+        <v>179</v>
       </c>
       <c r="D44" t="s">
-        <v>243</v>
+        <v>180</v>
       </c>
       <c r="E44" t="s">
-        <v>244</v>
+        <v>181</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>495</v>
+        <v>531</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B45">
+        <v>145</v>
+      </c>
+      <c r="C45" t="s">
+        <v>206</v>
+      </c>
+      <c r="D45" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" t="s">
+        <v>208</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>16</v>
+      </c>
+      <c r="B46">
+        <v>89</v>
+      </c>
+      <c r="C46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+      <c r="A47">
         <v>62</v>
       </c>
-      <c r="C45" t="s">
-        <v>218</v>
-      </c>
-      <c r="D45" t="s">
-        <v>219</v>
-      </c>
-      <c r="E45" t="s">
-        <v>220</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>-1</v>
-      </c>
-      <c r="B46">
-        <v>12444</v>
-      </c>
-      <c r="C46" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" t="s">
-        <v>6</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>0</v>
-      </c>
       <c r="B47">
+        <v>188</v>
+      </c>
+      <c r="C47" t="s">
+        <v>194</v>
+      </c>
+      <c r="D47" t="s">
+        <v>195</v>
+      </c>
+      <c r="E47" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>14</v>
+      </c>
+      <c r="B48">
+        <v>169</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" t="s">
+        <v>52</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>71</v>
       </c>
-      <c r="C47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>5</v>
-      </c>
-      <c r="B48">
-        <v>107</v>
-      </c>
-      <c r="C48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>60</v>
-      </c>
       <c r="B49">
-        <v>384</v>
+        <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="D49" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="E49" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+        <v>381</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="B50">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>211</v>
+        <v>49</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H50" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>72</v>
+      </c>
+      <c r="B51">
+        <v>88</v>
+      </c>
+      <c r="C51" t="s">
+        <v>224</v>
+      </c>
+      <c r="D51" t="s">
+        <v>225</v>
+      </c>
+      <c r="E51" t="s">
+        <v>226</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>80</v>
+      </c>
+      <c r="B52">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>248</v>
+      </c>
+      <c r="D52" t="s">
+        <v>249</v>
+      </c>
+      <c r="E52" t="s">
+        <v>250</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>68</v>
-      </c>
-      <c r="B51">
-        <v>169</v>
-      </c>
-      <c r="C51" t="s">
-        <v>212</v>
-      </c>
-      <c r="D51" t="s">
-        <v>213</v>
-      </c>
-      <c r="E51" t="s">
-        <v>214</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>85</v>
-      </c>
-      <c r="B52">
-        <v>1114</v>
-      </c>
-      <c r="C52" t="s">
-        <v>263</v>
-      </c>
-      <c r="D52" t="s">
-        <v>264</v>
-      </c>
-      <c r="E52" t="s">
-        <v>265</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>400</v>
+      <c r="G52" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="B53">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="E53" t="s">
-        <v>43</v>
+        <v>202</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>497</v>
+        <v>559</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B54">
-        <v>239</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="D54" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="E54" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>424</v>
+        <v>389</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>498</v>
+        <v>559</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="B55">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="C55" t="s">
-        <v>278</v>
+        <v>71</v>
       </c>
       <c r="D55" t="s">
-        <v>279</v>
+        <v>72</v>
       </c>
       <c r="E55" t="s">
-        <v>280</v>
+        <v>73</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>404</v>
+        <v>346</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+        <v>559</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B56">
-        <v>130</v>
+        <v>274</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="D56" t="s">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="E56" t="s">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>352</v>
+        <v>542</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>428</v>
+        <v>530</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="B57">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>239</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="E57" t="s">
-        <v>121</v>
+        <v>241</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>449</v>
+        <v>385</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H57" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="I57" s="9" t="s">
         <v>443</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B58">
-        <v>87</v>
+        <v>171</v>
       </c>
       <c r="C58" t="s">
-        <v>134</v>
+        <v>242</v>
       </c>
       <c r="D58" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>502</v>
+        <v>530</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="B59">
-        <v>118</v>
+        <v>239</v>
       </c>
       <c r="C59" t="s">
-        <v>113</v>
+        <v>287</v>
       </c>
       <c r="D59" t="s">
-        <v>114</v>
+        <v>288</v>
       </c>
       <c r="E59" t="s">
-        <v>115</v>
+        <v>289</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>449</v>
+        <v>546</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>503</v>
+        <v>530</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B60">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="C60" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="D60" t="s">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="E60" t="s">
-        <v>133</v>
+        <v>238</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>504</v>
+        <v>530</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="B61">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>251</v>
       </c>
       <c r="D61" t="s">
-        <v>102</v>
+        <v>252</v>
       </c>
       <c r="E61" t="s">
-        <v>103</v>
+        <v>253</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>449</v>
+        <v>547</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>505</v>
+        <v>530</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="B62">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>269</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
       <c r="E62" t="s">
-        <v>127</v>
+        <v>271</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>449</v>
+        <v>557</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="I62" s="8" t="s">
-        <v>506</v>
+        <v>530</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="B63">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C63" t="s">
-        <v>236</v>
+        <v>92</v>
       </c>
       <c r="D63" t="s">
-        <v>237</v>
+        <v>93</v>
       </c>
       <c r="E63" t="s">
-        <v>238</v>
+        <v>94</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>422</v>
+        <v>353</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>507</v>
+        <v>528</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="B64">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="C64" t="s">
-        <v>251</v>
+        <v>98</v>
       </c>
       <c r="D64" t="s">
-        <v>252</v>
+        <v>99</v>
       </c>
       <c r="E64" t="s">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>396</v>
+        <v>539</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>508</v>
+        <v>528</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="B65">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C65" t="s">
-        <v>167</v>
+        <v>311</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="E65" t="s">
-        <v>169</v>
+        <v>313</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I65" s="8" t="s">
-        <v>509</v>
+        <v>528</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B66">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="D66" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="E66" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>558</v>
+        <v>354</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>436</v>
+        <v>528</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="I66" s="8" t="s">
-        <v>510</v>
+        <v>355</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B67">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="E67" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I67" s="8" t="s">
-        <v>511</v>
+        <v>528</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="B68">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C68" t="s">
-        <v>149</v>
+        <v>302</v>
       </c>
       <c r="D68" t="s">
-        <v>150</v>
+        <v>303</v>
       </c>
       <c r="E68" t="s">
-        <v>151</v>
+        <v>304</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="I68" s="8" t="s">
-        <v>512</v>
+        <v>528</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="B69">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="C69" t="s">
-        <v>302</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>303</v>
+        <v>105</v>
       </c>
       <c r="E69" t="s">
-        <v>304</v>
+        <v>106</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>410</v>
+        <v>550</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="I69" s="8" t="s">
-        <v>513</v>
+        <v>528</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="B70">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="C70" t="s">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="D70" t="s">
-        <v>84</v>
+        <v>246</v>
       </c>
       <c r="E70" t="s">
-        <v>85</v>
+        <v>247</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>353</v>
+        <v>551</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="I70" s="8" t="s">
-        <v>514</v>
+        <v>528</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B71">
-        <v>73</v>
+        <v>899</v>
       </c>
       <c r="C71" t="s">
-        <v>179</v>
+        <v>257</v>
       </c>
       <c r="D71" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="E71" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I71" s="8" t="s">
-        <v>515</v>
+        <v>535</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B72">
-        <v>266</v>
+        <v>88</v>
       </c>
       <c r="C72" t="s">
-        <v>104</v>
+        <v>233</v>
       </c>
       <c r="D72" t="s">
-        <v>105</v>
+        <v>234</v>
       </c>
       <c r="E72" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="I72" s="8" t="s">
-        <v>516</v>
+        <v>535</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B73">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="D73" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="E73" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>384</v>
+        <v>543</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I73" s="8" t="s">
-        <v>517</v>
+        <v>535</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B74">
-        <v>345</v>
+        <v>188</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
+        <v>308</v>
       </c>
       <c r="D74" t="s">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="E74" t="s">
-        <v>205</v>
+        <v>310</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="I74" s="8" t="s">
-        <v>518</v>
+        <v>535</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B75">
-        <v>188</v>
+        <v>315</v>
       </c>
       <c r="C75" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D75" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E75" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>411</v>
+        <v>554</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>519</v>
+        <v>535</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B76">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="C76" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="D76" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="E76" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>362</v>
+        <v>552</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I76" s="8" t="s">
-        <v>520</v>
+        <v>533</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="B77">
-        <v>59</v>
+        <v>605</v>
       </c>
       <c r="C77" t="s">
-        <v>305</v>
+        <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>306</v>
+        <v>39</v>
       </c>
       <c r="E77" t="s">
-        <v>307</v>
+        <v>40</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>522</v>
+        <v>558</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>521</v>
+        <v>533</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="B78">
-        <v>387</v>
+        <v>158</v>
       </c>
       <c r="C78" t="s">
-        <v>317</v>
+        <v>68</v>
       </c>
       <c r="D78" t="s">
-        <v>318</v>
+        <v>69</v>
       </c>
       <c r="E78" t="s">
-        <v>319</v>
+        <v>70</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>414</v>
+        <v>345</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="I78" s="8" t="s">
-        <v>523</v>
+        <v>408</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="B79">
-        <v>281</v>
+        <v>67</v>
       </c>
       <c r="C79" t="s">
-        <v>314</v>
+        <v>119</v>
       </c>
       <c r="D79" t="s">
-        <v>315</v>
+        <v>120</v>
       </c>
       <c r="E79" t="s">
-        <v>316</v>
+        <v>121</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="I79" s="8" t="s">
-        <v>524</v>
+        <v>408</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B80">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="C80" t="s">
-        <v>245</v>
+        <v>134</v>
       </c>
       <c r="D80" t="s">
-        <v>246</v>
+        <v>135</v>
       </c>
       <c r="E80" t="s">
-        <v>247</v>
+        <v>136</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="I80" s="8" t="s">
-        <v>525</v>
+        <v>408</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="B81">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="C81" t="s">
-        <v>215</v>
+        <v>113</v>
       </c>
       <c r="D81" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="E81" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I81" s="8" t="s">
-        <v>526</v>
+        <v>408</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B82">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="C82" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="D82" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="E82" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>371</v>
+        <v>418</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>527</v>
+        <v>408</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B83">
-        <v>148</v>
+        <v>209</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="E83" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="I83" s="8" t="s">
-        <v>528</v>
+        <v>408</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B84">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D84" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E84" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>363</v>
+        <v>418</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="I84" s="8" t="s">
-        <v>529</v>
+        <v>408</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="B85">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C85" t="s">
-        <v>200</v>
+        <v>116</v>
       </c>
       <c r="D85" t="s">
-        <v>201</v>
+        <v>117</v>
       </c>
       <c r="E85" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="I85" s="8" t="s">
-        <v>530</v>
+        <v>408</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4379,649 +4410,625 @@
         <v>124</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="I86" s="8" t="s">
-        <v>532</v>
+        <v>500</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B87">
-        <v>64</v>
+        <v>254</v>
       </c>
       <c r="C87" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I87" s="8" t="s">
-        <v>533</v>
+        <v>407</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B88">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C88" t="s">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="D88" t="s">
-        <v>57</v>
+        <v>228</v>
       </c>
       <c r="E88" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>345</v>
+        <v>396</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I88" s="8" t="s">
-        <v>534</v>
+        <v>407</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B89">
-        <v>315</v>
+        <v>145</v>
       </c>
       <c r="C89" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="D89" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="E89" t="s">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="I89" s="8" t="s">
-        <v>535</v>
+        <v>407</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B90">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C90" t="s">
-        <v>194</v>
+        <v>299</v>
       </c>
       <c r="D90" t="s">
-        <v>195</v>
+        <v>300</v>
       </c>
       <c r="E90" t="s">
-        <v>196</v>
+        <v>301</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I90" s="8" t="s">
-        <v>536</v>
+        <v>407</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="B91">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="C91" t="s">
-        <v>50</v>
+        <v>215</v>
       </c>
       <c r="D91" t="s">
-        <v>51</v>
+        <v>216</v>
       </c>
       <c r="E91" t="s">
-        <v>52</v>
+        <v>217</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I91" s="8" t="s">
-        <v>537</v>
+        <v>407</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="B92">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="C92" t="s">
-        <v>260</v>
+        <v>158</v>
       </c>
       <c r="D92" t="s">
-        <v>261</v>
+        <v>159</v>
       </c>
       <c r="E92" t="s">
-        <v>262</v>
+        <v>160</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="I92" s="8" t="s">
-        <v>538</v>
+        <v>407</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="B93">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C93" t="s">
-        <v>284</v>
+        <v>173</v>
       </c>
       <c r="D93" t="s">
-        <v>285</v>
+        <v>174</v>
       </c>
       <c r="E93" t="s">
-        <v>286</v>
+        <v>175</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>415</v>
+        <v>367</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="I93" s="8" t="s">
-        <v>539</v>
+        <v>407</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="B94">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C94" t="s">
-        <v>254</v>
+        <v>143</v>
       </c>
       <c r="D94" t="s">
-        <v>255</v>
+        <v>144</v>
       </c>
       <c r="E94" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I94" s="8" t="s">
-        <v>540</v>
+        <v>407</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="B95">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C95" t="s">
-        <v>77</v>
+        <v>329</v>
       </c>
       <c r="D95" t="s">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="E95" t="s">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>351</v>
+        <v>527</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I95" s="8" t="s">
-        <v>541</v>
+        <v>407</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="B96">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="C96" t="s">
-        <v>269</v>
+        <v>146</v>
       </c>
       <c r="D96" t="s">
-        <v>270</v>
+        <v>147</v>
       </c>
       <c r="E96" t="s">
-        <v>271</v>
+        <v>148</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>402</v>
+        <v>361</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="I96" s="8" t="s">
-        <v>542</v>
+        <v>407</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="B97">
-        <v>605</v>
+        <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>38</v>
+        <v>293</v>
       </c>
       <c r="D97" t="s">
-        <v>39</v>
+        <v>294</v>
       </c>
       <c r="E97" t="s">
-        <v>40</v>
+        <v>295</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>417</v>
+        <v>395</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="I97" s="8" t="s">
-        <v>543</v>
+        <v>407</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B98">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C98" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="D98" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="E98" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I98" s="8" t="s">
-        <v>173</v>
+        <v>407</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B99">
-        <v>156</v>
+        <v>1285</v>
       </c>
       <c r="C99" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E99" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>349</v>
+        <v>405</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="I99" s="8" t="s">
-        <v>544</v>
+        <v>407</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="B100">
-        <v>170</v>
+        <v>305</v>
       </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>281</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
+        <v>282</v>
       </c>
       <c r="E100" t="s">
-        <v>46</v>
+        <v>283</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="I100" s="8" t="s">
-        <v>545</v>
+        <v>407</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="B101">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C101" t="s">
-        <v>143</v>
+        <v>290</v>
       </c>
       <c r="D101" t="s">
-        <v>144</v>
+        <v>291</v>
       </c>
       <c r="E101" t="s">
-        <v>145</v>
+        <v>292</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I101" s="8" t="s">
-        <v>546</v>
+        <v>407</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B102">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="C102" t="s">
-        <v>329</v>
+        <v>272</v>
       </c>
       <c r="D102" t="s">
-        <v>330</v>
+        <v>273</v>
       </c>
       <c r="E102" t="s">
-        <v>331</v>
+        <v>274</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>556</v>
+        <v>409</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I102" s="8" t="s">
-        <v>547</v>
+        <v>407</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B103">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="C103" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D103" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E103" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I103" s="8" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>95</v>
+        <v>-1</v>
       </c>
       <c r="B104">
-        <v>120</v>
+        <v>12444</v>
       </c>
       <c r="C104" t="s">
-        <v>293</v>
+        <v>5</v>
       </c>
       <c r="D104" t="s">
-        <v>294</v>
+        <v>6</v>
       </c>
       <c r="E104" t="s">
-        <v>295</v>
+        <v>7</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I104" s="8" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B105">
+        <v>71</v>
+      </c>
+      <c r="C105" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>5</v>
+      </c>
+      <c r="B106">
+        <v>107</v>
+      </c>
+      <c r="C106" t="s">
+        <v>23</v>
+      </c>
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>60</v>
+      </c>
+      <c r="B107">
+        <v>384</v>
+      </c>
+      <c r="C107" t="s">
+        <v>188</v>
+      </c>
+      <c r="D107" t="s">
+        <v>189</v>
+      </c>
+      <c r="E107" t="s">
+        <v>190</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A108">
         <v>67</v>
       </c>
-      <c r="C105" t="s">
-        <v>140</v>
-      </c>
-      <c r="D105" t="s">
-        <v>141</v>
-      </c>
-      <c r="E105" t="s">
-        <v>142</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I105" s="8" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="16" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>2</v>
-      </c>
-      <c r="B106">
-        <v>1285</v>
-      </c>
-      <c r="C106" t="s">
-        <v>14</v>
-      </c>
-      <c r="D106" t="s">
-        <v>15</v>
-      </c>
-      <c r="E106" t="s">
-        <v>16</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="16" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>91</v>
-      </c>
-      <c r="B107">
-        <v>305</v>
-      </c>
-      <c r="C107" t="s">
-        <v>281</v>
-      </c>
-      <c r="D107" t="s">
-        <v>282</v>
-      </c>
-      <c r="E107" t="s">
-        <v>283</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I107" s="8" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="16" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>94</v>
-      </c>
       <c r="B108">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C108" t="s">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="D108" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="E108" t="s">
-        <v>292</v>
+        <v>211</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I108" s="8" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+      <c r="H108" s="7" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B109">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C109" t="s">
-        <v>272</v>
+        <v>212</v>
       </c>
       <c r="D109" t="s">
-        <v>273</v>
+        <v>213</v>
       </c>
       <c r="E109" t="s">
-        <v>274</v>
+        <v>214</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>426</v>
+        <v>334</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="I109" s="8" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="B110">
-        <v>61</v>
+        <v>1114</v>
       </c>
       <c r="C110" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="D110" t="s">
-        <v>138</v>
+        <v>264</v>
       </c>
       <c r="E110" t="s">
-        <v>139</v>
+        <v>265</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I110" s="8" t="s">
-        <v>555</v>
+        <v>334</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H110">
-      <sortCondition ref="F1:F110"/>
+  <autoFilter ref="A1:I110" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I110">
+      <sortCondition ref="G1:G110"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/interim/cluster_review.xlsx
+++ b/interim/cluster_review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilya/chat-geospatial/interim/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A886A0-5B63-D644-810A-41C5032113AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19A4771-FE97-8445-9B45-D5430365B466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7220" yWindow="600" windowWidth="33480" windowHeight="26900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14060" yWindow="600" windowWidth="33480" windowHeight="26900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1249,9 +1249,6 @@
     <t>group</t>
   </si>
   <si>
-    <t>Writing and ideation</t>
-  </si>
-  <si>
     <t>Trip planning</t>
   </si>
   <si>
@@ -1657,9 +1654,6 @@
     <t>Planets &amp; space*</t>
   </si>
   <si>
-    <t>GDP &amp; national economies*</t>
-  </si>
-  <si>
     <t>Historical battles &amp; wars*</t>
   </si>
   <si>
@@ -1687,9 +1681,6 @@
     <t>Time zones*</t>
   </si>
   <si>
-    <t>UK &amp; French monarchs / heads of state*</t>
-  </si>
-  <si>
     <t>University rankings*</t>
   </si>
   <si>
@@ -1706,6 +1697,15 @@
   </si>
   <si>
     <t>Misc</t>
+  </si>
+  <si>
+    <t>GDP &amp; national economies</t>
+  </si>
+  <si>
+    <t>Kings and monarchs*</t>
+  </si>
+  <si>
+    <t>Writing &amp; ideation</t>
   </si>
 </sst>
 </file>
@@ -2164,7 +2164,7 @@
         <v>333</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2184,13 +2184,13 @@
         <v>154</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2213,13 +2213,13 @@
         <v>366</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>372</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2242,10 +2242,10 @@
         <v>366</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2268,10 +2268,10 @@
         <v>366</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2294,13 +2294,13 @@
         <v>366</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>372</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2323,10 +2323,10 @@
         <v>387</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2346,13 +2346,13 @@
         <v>172</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2372,16 +2372,16 @@
         <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2401,16 +2401,16 @@
         <v>22</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2430,13 +2430,13 @@
         <v>307</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2459,10 +2459,10 @@
         <v>402</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2485,10 +2485,10 @@
         <v>401</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2511,10 +2511,10 @@
         <v>403</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2537,10 +2537,10 @@
         <v>373</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2563,13 +2563,13 @@
         <v>404</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2592,10 +2592,10 @@
         <v>404</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2618,10 +2618,10 @@
         <v>356</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2644,10 +2644,10 @@
         <v>364</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2670,10 +2670,10 @@
         <v>391</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2696,10 +2696,10 @@
         <v>339</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2722,10 +2722,10 @@
         <v>347</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2748,10 +2748,10 @@
         <v>369</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2774,10 +2774,10 @@
         <v>352</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2800,10 +2800,10 @@
         <v>351</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2826,10 +2826,10 @@
         <v>359</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2852,10 +2852,10 @@
         <v>380</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2878,10 +2878,10 @@
         <v>340</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2904,10 +2904,10 @@
         <v>392</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2930,10 +2930,10 @@
         <v>349</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2956,10 +2956,10 @@
         <v>383</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -2982,10 +2982,10 @@
         <v>357</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3008,10 +3008,10 @@
         <v>343</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3034,10 +3034,10 @@
         <v>348</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3060,10 +3060,10 @@
         <v>337</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3086,10 +3086,10 @@
         <v>350</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3112,10 +3112,10 @@
         <v>338</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3138,10 +3138,10 @@
         <v>376</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3164,10 +3164,10 @@
         <v>341</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3187,13 +3187,13 @@
         <v>178</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3213,13 +3213,13 @@
         <v>166</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3239,16 +3239,16 @@
         <v>61</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3268,13 +3268,13 @@
         <v>64</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3297,10 +3297,10 @@
         <v>368</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3323,10 +3323,10 @@
         <v>375</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3346,13 +3346,13 @@
         <v>58</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3372,13 +3372,13 @@
         <v>196</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3398,13 +3398,13 @@
         <v>52</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3427,7 +3427,7 @@
         <v>381</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>221</v>
@@ -3453,10 +3453,10 @@
         <v>342</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3479,10 +3479,10 @@
         <v>382</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3505,10 +3505,10 @@
         <v>386</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3531,10 +3531,10 @@
         <v>374</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3557,10 +3557,10 @@
         <v>389</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3583,10 +3583,10 @@
         <v>346</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
@@ -3606,13 +3606,13 @@
         <v>232</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3635,10 +3635,10 @@
         <v>385</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3658,13 +3658,13 @@
         <v>244</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3684,13 +3684,13 @@
         <v>289</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3710,13 +3710,13 @@
         <v>238</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3736,13 +3736,13 @@
         <v>253</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3762,13 +3762,13 @@
         <v>271</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3791,10 +3791,10 @@
         <v>353</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3814,13 +3814,13 @@
         <v>100</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3843,7 +3843,7 @@
         <v>400</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>311</v>
@@ -3869,13 +3869,13 @@
         <v>354</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>355</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3898,10 +3898,10 @@
         <v>363</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3924,10 +3924,10 @@
         <v>398</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3947,13 +3947,13 @@
         <v>106</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -3973,13 +3973,13 @@
         <v>247</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4002,10 +4002,10 @@
         <v>388</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4028,10 +4028,10 @@
         <v>384</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4051,13 +4051,13 @@
         <v>268</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4080,10 +4080,10 @@
         <v>399</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4103,13 +4103,13 @@
         <v>328</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4129,13 +4129,13 @@
         <v>37</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4155,13 +4155,13 @@
         <v>40</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4184,13 +4184,13 @@
         <v>345</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>344</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4210,16 +4210,16 @@
         <v>121</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4239,16 +4239,16 @@
         <v>136</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4268,16 +4268,16 @@
         <v>115</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4297,16 +4297,16 @@
         <v>133</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4326,16 +4326,16 @@
         <v>103</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4355,16 +4355,16 @@
         <v>127</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4387,10 +4387,10 @@
         <v>358</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4410,16 +4410,16 @@
         <v>124</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H86" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="I86" s="9" t="s">
         <v>500</v>
-      </c>
-      <c r="I86" s="9" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4442,10 +4442,10 @@
         <v>396</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4468,10 +4468,10 @@
         <v>396</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4494,10 +4494,10 @@
         <v>396</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4520,10 +4520,10 @@
         <v>397</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4546,10 +4546,10 @@
         <v>379</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4572,10 +4572,10 @@
         <v>365</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4598,7 +4598,7 @@
         <v>367</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I93" s="9" t="s">
         <v>173</v>
@@ -4624,10 +4624,10 @@
         <v>362</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4647,13 +4647,13 @@
         <v>331</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4676,10 +4676,10 @@
         <v>361</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4702,10 +4702,10 @@
         <v>395</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4728,10 +4728,10 @@
         <v>360</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4754,10 +4754,10 @@
         <v>405</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4780,10 +4780,10 @@
         <v>393</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4806,10 +4806,10 @@
         <v>394</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4829,16 +4829,16 @@
         <v>274</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="16" x14ac:dyDescent="0.25">
@@ -4861,10 +4861,10 @@
         <v>370</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">

--- a/interim/cluster_review.xlsx
+++ b/interim/cluster_review.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilya/chat-geospatial/interim/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19A4771-FE97-8445-9B45-D5430365B466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B49DE90-090F-7F4B-B76E-F76540D877A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14060" yWindow="600" windowWidth="33480" windowHeight="26900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3869,7 +3869,7 @@
         <v>354</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>527</v>
+        <v>407</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>355</v>
